--- a/output/cv_percetage_no_outlier.xlsx
+++ b/output/cv_percetage_no_outlier.xlsx
@@ -475,23 +475,23 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6.605450336729743</v>
+        <v>4.761815417866115</v>
       </c>
       <c r="C2" t="n">
-        <v>3.394428310468495</v>
+        <v>2.454192696952327</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.1882663921270495</v>
       </c>
       <c r="F2" t="n">
-        <v>50.19971445591812</v>
+        <v>61.9569408596556</v>
       </c>
       <c r="G2" t="n">
-        <v>20.20305089104422</v>
+        <v>76.20210104768525</v>
       </c>
       <c r="H2" t="n">
-        <v>85.29882064773334</v>
+        <v>66.39574784913388</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         <v>80.81220356417687</v>
       </c>
       <c r="H3" t="n">
-        <v>44.04927489358822</v>
+        <v>42.42721463665282</v>
       </c>
     </row>
     <row r="4">
